--- a/paper simu/ham_count.xlsx
+++ b/paper simu/ham_count.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baptiste\Documents\PhD\Projects\RL_CS\paper simu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C14FC18-C80C-4DC5-941A-E829E442E6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969BD73A-16BC-4A85-82BF-8C4FD4103F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39D90E8F-B3C5-4DD0-9676-C2F73D295ECC}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +188,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Lat"/>
     </font>
   </fonts>
   <fills count="33">
@@ -531,8 +536,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -580,6 +586,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF000000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -605,9 +616,87 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Latin modern"/>
+              </a:rPr>
+              <a:t>(a) Annealing</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14127971867594222"/>
+          <c:y val="8.8888811589289948E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12167183956374385"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.84979395051346729"/>
+          <c:h val="0.76492418964810094"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -627,11 +716,11 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -691,25 +780,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>52.26</c:v>
+                  <c:v>45.78</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.78</c:v>
+                  <c:v>35.56</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.6</c:v>
+                  <c:v>13.98</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.74</c:v>
+                  <c:v>3.98</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.06</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15.36</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -772,23 +861,49 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
                   <a:t>Hamming distance</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
                   <a:t> to optimal</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-US" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.33567211790833834"/>
+              <c:y val="0.92228258967629051"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -809,9 +924,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -840,16 +955,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -866,6 +978,8 @@
         <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -873,9 +987,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -892,23 +1005,34 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Percentage of estimates</a:t>
+                  <a:rPr lang="en-US" sz="1200" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -924,14 +1048,11 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -954,16 +1075,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -975,8 +1093,10 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -997,12 +1117,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1020,7 +1135,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1039,9 +1154,87 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Latin modern"/>
+              </a:rPr>
+              <a:t>(b) Random</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14127971867594222"/>
+          <c:y val="8.8888811589289948E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12167183956374385"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.84979395051346729"/>
+          <c:h val="0.76492418964810094"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1049,12 +1242,23 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ham_count!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>random</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -1114,25 +1318,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>21.32</c:v>
+                  <c:v>6.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28.6</c:v>
+                  <c:v>27.12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.92</c:v>
+                  <c:v>34.380000000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.86</c:v>
+                  <c:v>22.76</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.48</c:v>
+                  <c:v>8.7799999999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17.72</c:v>
+                  <c:v>0.74</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.1</c:v>
+                  <c:v>0.14000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -1157,7 +1361,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-483A-4420-89E2-4C5B3E10675F}"/>
+              <c16:uniqueId val="{00000000-28E8-4B73-9A69-21475272D80E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1171,11 +1375,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="319442399"/>
-        <c:axId val="319440479"/>
+        <c:axId val="319415039"/>
+        <c:axId val="319415999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="319442399"/>
+        <c:axId val="319415039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1195,25 +1399,49 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Hamming distance to optimal</a:t>
+                  <a:t>Hamming distance</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t> to optimal</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.33567211790833834"/>
+              <c:y val="0.92228258967629051"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1234,9 +1462,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1265,22 +1493,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="319440479"/>
+        <c:crossAx val="319415999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1288,9 +1513,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="319440479"/>
+        <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1298,9 +1525,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1314,47 +1540,37 @@
               <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:buClrTx/>
-                  <a:buSzTx/>
-                  <a:buFontTx/>
-                  <a:buNone/>
-                  <a:tabLst/>
+                <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Percentage of estimates</a:t>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1367,31 +1583,14 @@
             <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-                <a:lnSpc>
-                  <a:spcPct val="100000"/>
-                </a:lnSpc>
-                <a:spcBef>
-                  <a:spcPts val="0"/>
-                </a:spcBef>
-                <a:spcAft>
-                  <a:spcPts val="0"/>
-                </a:spcAft>
-                <a:buClrTx/>
-                <a:buSzTx/>
-                <a:buFontTx/>
-                <a:buNone/>
-                <a:tabLst/>
+              <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:sysClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1414,29 +1613,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="319442399"/>
+        <c:crossAx val="319415039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1457,12 +1655,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1480,7 +1673,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1492,16 +1685,94 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="105"/>
+      <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="5"/>
+      <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Latin modern"/>
+              </a:rPr>
+              <a:t>(c) Quadruplets sketch</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14127971867594222"/>
+          <c:y val="8.8888811589289948E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12167183956374385"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.84979395051346729"/>
+          <c:h val="0.76492418964810094"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1509,12 +1780,23 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ham_count!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quadruplets</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -1574,25 +1856,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>48.14</c:v>
+                  <c:v>57.56</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.02</c:v>
+                  <c:v>33.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.88</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.66</c:v>
+                  <c:v>0.94</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.08</c:v>
+                  <c:v>0.18</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.04</c:v>
+                  <c:v>0.04</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.18</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -1617,7 +1899,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3CD3-4C0B-8501-66ABCE37E2FC}"/>
+              <c16:uniqueId val="{00000000-0690-490F-AF81-2270B1389D48}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1631,11 +1913,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="319434719"/>
-        <c:axId val="319435199"/>
+        <c:axId val="319415039"/>
+        <c:axId val="319415999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="319434719"/>
+        <c:axId val="319415039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1655,25 +1937,49 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Hamming distance to optimal</a:t>
+                  <a:t>Hamming distance</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t> to optimal</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.33567211790833834"/>
+              <c:y val="0.92228258967629051"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1694,9 +2000,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1725,22 +2031,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="319435199"/>
+        <c:crossAx val="319415999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1748,9 +2051,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="319435199"/>
+        <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1758,9 +2063,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1777,30 +2081,34 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Percentage of estimates</a:t>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1816,14 +2124,11 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1846,29 +2151,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="319434719"/>
+        <c:crossAx val="319415039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1889,12 +2193,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1912,7 +2211,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1931,9 +2230,87 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Latin modern"/>
+              </a:rPr>
+              <a:t>(d) Quintuplets sketch</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14127971867594222"/>
+          <c:y val="8.8888811589289948E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12167183956374385"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.84979395051346729"/>
+          <c:h val="0.76492418964810094"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1941,12 +2318,23 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ham_count!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quintuplets</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="00B0F0"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -2006,25 +2394,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>62.74</c:v>
+                  <c:v>48.92</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.100000000000001</c:v>
+                  <c:v>36.380000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.24</c:v>
+                  <c:v>11.28</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.72</c:v>
+                  <c:v>3.06</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.14000000000000001</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.18</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.88</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -2049,7 +2437,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-57F3-4AE2-A9F6-91967FC0CE2E}"/>
+              <c16:uniqueId val="{00000000-E9D3-4E58-AE48-C45A8E8115BA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2063,11 +2451,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="319443839"/>
-        <c:axId val="319444799"/>
+        <c:axId val="319415039"/>
+        <c:axId val="319415999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="319443839"/>
+        <c:axId val="319415039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2087,25 +2475,49 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Hamming distance to optimal</a:t>
+                  <a:t>Hamming distance</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t> to optimal</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.33567211790833834"/>
+              <c:y val="0.92228258967629051"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2126,9 +2538,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2157,22 +2569,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="319444799"/>
+        <c:crossAx val="319415999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2180,9 +2589,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="319444799"/>
+        <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2190,9 +2601,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -2209,30 +2619,34 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Percentage of estimates</a:t>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2248,14 +2662,11 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2278,29 +2689,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="319443839"/>
+        <c:crossAx val="319415039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -2321,12 +2731,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -2344,7 +2749,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -2430,8 +2835,42 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -4491,16 +4930,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>4761</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4527,27 +4966,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>4761</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C36A200-8F06-38BB-9BEC-2E97C784988E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2846CA-5E58-428D-9085-58187EDE274A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4563,27 +5004,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>14286</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="10" name="Chart 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20303BC6-FA58-E8AD-21F1-D39D266E9AF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F78944F7-F188-4705-BC70-C7C5001027A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4600,26 +5043,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>14286</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6">
+        <xdr:cNvPr id="11" name="Chart 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BF7D8FC-C8FA-5853-99CE-E2C8198EF936}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7406AC2A-1F90-47DC-9195-971A96D35499}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4953,8 +5398,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14B590B-B299-495B-AC4E-1431A9EDC904}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
@@ -4963,7 +5408,7 @@
     <col min="5" max="5" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4980,273 +5425,274 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2613</v>
+        <v>2289</v>
       </c>
       <c r="C2">
-        <v>1066</v>
+        <v>304</v>
       </c>
       <c r="D2">
-        <v>2407</v>
+        <v>2878</v>
       </c>
       <c r="E2">
-        <v>3137</v>
-      </c>
+        <v>2446</v>
+      </c>
+      <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1139</v>
+        <v>1778</v>
       </c>
       <c r="C3">
-        <v>1430</v>
+        <v>1356</v>
       </c>
       <c r="D3">
-        <v>1201</v>
+        <v>1689</v>
       </c>
       <c r="E3">
-        <v>955</v>
+        <v>1819</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>130</v>
+        <v>699</v>
       </c>
       <c r="C4">
-        <v>646</v>
+        <v>1719</v>
       </c>
       <c r="D4">
-        <v>244</v>
+        <v>375</v>
       </c>
       <c r="E4">
-        <v>62</v>
+        <v>564</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="C5">
-        <v>393</v>
+        <v>1138</v>
       </c>
       <c r="D5">
-        <v>283</v>
+        <v>47</v>
       </c>
       <c r="E5">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C6">
-        <v>174</v>
+        <v>439</v>
       </c>
       <c r="D6">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>768</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>886</v>
+        <v>37</v>
       </c>
       <c r="D7">
-        <v>602</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>509</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>405</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>194</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>0</v>
       </c>
       <c r="B11">
         <f>B2/50</f>
-        <v>52.26</v>
+        <v>45.78</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:E11" si="0">C2/50</f>
-        <v>21.32</v>
+        <v>6.08</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>48.14</v>
+        <v>57.56</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>62.74</v>
+        <v>48.92</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12">
         <f t="shared" ref="B12:E17" si="1">B3/50</f>
-        <v>22.78</v>
+        <v>35.56</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>28.6</v>
+        <v>27.12</v>
       </c>
       <c r="D12">
         <f t="shared" si="1"/>
-        <v>24.02</v>
+        <v>33.78</v>
       </c>
       <c r="E12">
         <f t="shared" si="1"/>
-        <v>19.100000000000001</v>
+        <v>36.380000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>13.98</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>12.92</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="D13">
         <f t="shared" si="1"/>
-        <v>4.88</v>
+        <v>7.5</v>
       </c>
       <c r="E13">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>11.28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>3</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>1.74</v>
+        <v>3.98</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>7.86</v>
+        <v>22.76</v>
       </c>
       <c r="D14">
         <f t="shared" si="1"/>
-        <v>5.66</v>
+        <v>0.94</v>
       </c>
       <c r="E14">
         <f t="shared" si="1"/>
-        <v>2.72</v>
+        <v>3.06</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>4</v>
       </c>
       <c r="B15">
         <f t="shared" si="1"/>
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
-        <v>3.48</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="D15">
         <f t="shared" si="1"/>
-        <v>1.08</v>
+        <v>0.18</v>
       </c>
       <c r="E15">
         <f t="shared" si="1"/>
-        <v>0.14000000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>5</v>
       </c>
       <c r="B16">
         <f t="shared" si="1"/>
-        <v>15.36</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
-        <v>17.72</v>
+        <v>0.74</v>
       </c>
       <c r="D16">
         <f t="shared" si="1"/>
-        <v>12.04</v>
+        <v>0.04</v>
       </c>
       <c r="E16">
         <f t="shared" si="1"/>
-        <v>10.18</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>6</v>
       </c>
       <c r="B17">
         <f t="shared" si="1"/>
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
-        <v>8.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <f t="shared" si="1"/>
-        <v>3.88</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>7</v>
       </c>
@@ -5263,7 +5709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>8</v>
       </c>
@@ -5280,7 +5726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>9</v>
       </c>
@@ -5297,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>10</v>
       </c>
@@ -5314,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>11</v>
       </c>
@@ -5331,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>12</v>
       </c>
@@ -5346,6 +5792,42 @@
       </c>
       <c r="E23">
         <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25">
+        <f>B11+B12</f>
+        <v>81.34</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ref="C25:E25" si="2">C11+C12</f>
+        <v>33.200000000000003</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="2"/>
+        <v>91.34</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="2"/>
+        <v>85.300000000000011</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26">
+        <f>B25+B13</f>
+        <v>95.320000000000007</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:E26" si="3">C25+C13</f>
+        <v>67.580000000000013</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="3"/>
+        <v>98.84</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="3"/>
+        <v>96.580000000000013</v>
       </c>
     </row>
   </sheetData>
